--- a/backend/Mandanten/Elektroniker_Testbetrieb/Lieferscheine/lieferscheine.xlsx
+++ b/backend/Mandanten/Elektroniker_Testbetrieb/Lieferscheine/lieferscheine.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -511,6 +511,38 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Oma_Erna</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Oma_Erna</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/Mandanten/Elektroniker_Testbetrieb/Lieferscheine/lieferscheine.xlsx
+++ b/backend/Mandanten/Elektroniker_Testbetrieb/Lieferscheine/lieferscheine.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,27 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
-        <bgColor rgb="00D3D3D3"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,13 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,16 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -482,66 +459,122 @@
           <t>Items</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Angebot</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PDF_Path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>LS-2025-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.12.2025</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Oma_Erna</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Offen</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Oma_Erna</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PROT-2026-999</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>04.01.2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Testkunde 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[{"text": "Wartung durchgef\u00fchrt", "menge": 1}, {"text": "Dichtungen erneuert", "menge": 3}]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANG-2026-001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mandanten/Elektroniker_Testbetrieb/Lieferscheine/PROT-2026-999.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PROT-2026-001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>04.01.2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Oma_Erna</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ANG-2026-001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mandanten/Elektroniker_Testbetrieb/Lieferscheine/Lieferschein_PROT-2026-001_1767560752.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
